--- a/data/gummibears.xlsx
+++ b/data/gummibears.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74446464-45A4-AA4E-B181-143BF6C8634A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D75E7B4-F93B-7149-9320-FDA4ED612143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2300" yWindow="600" windowWidth="30960" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="30">
   <si>
     <t>m</t>
   </si>
@@ -644,7 +643,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q1069"/>
+  <dimension ref="A1:Q1099"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -49910,6 +49909,1414 @@
         <v>2</v>
       </c>
     </row>
+    <row r="1070" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1070" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1070" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1070" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1070" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1070" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1070" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1070" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1070" s="6">
+        <v>3</v>
+      </c>
+      <c r="I1070" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1070" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1070" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1070" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1070" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1070" s="6">
+        <v>167</v>
+      </c>
+      <c r="O1070" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1071" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1071" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1071" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1071" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1071" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1071" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1071" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1071" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1071" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1071" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1071" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1071" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1071" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1071" s="6">
+        <v>168</v>
+      </c>
+      <c r="O1071" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1072" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1072" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1072" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1072" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1072" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1072" s="6">
+        <v>4</v>
+      </c>
+      <c r="G1072" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1072" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1072" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1072" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1072" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1072" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1072" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1072" s="6">
+        <v>179</v>
+      </c>
+      <c r="O1072" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1073" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1073" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1073" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1073" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1073" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1073" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1073" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1073" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1073" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1073" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1073" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1073" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1073" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1073" s="6">
+        <v>190</v>
+      </c>
+      <c r="O1073" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1074" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1074" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1074" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1074" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1074" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1074" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1074" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1074" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1074" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1074" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1074" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1074" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1074" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1074" s="6">
+        <v>190</v>
+      </c>
+      <c r="O1074" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1075" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1075" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1075" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1075" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1075" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1075" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1075" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1075" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1075" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1075" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1075" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1075" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1075" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1075" s="6">
+        <v>162</v>
+      </c>
+      <c r="O1075" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1076" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1076" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1076" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1076" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1076" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1076" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1076" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1076" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1076" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1076" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1076" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1076" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1076" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1076" s="6">
+        <v>190</v>
+      </c>
+      <c r="O1076" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1077" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1077" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1077" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1077" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1077" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1077" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1077" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1077" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1077" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1077" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1077" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1077" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1077" s="6">
+        <v>26</v>
+      </c>
+      <c r="N1077" s="6">
+        <v>165</v>
+      </c>
+      <c r="O1077" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1078" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1078" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1078" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1078" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1078" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1078" s="6">
+        <v>4</v>
+      </c>
+      <c r="G1078" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1078" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1078" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1078" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1078" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1078" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1078" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1078" s="6">
+        <v>182</v>
+      </c>
+      <c r="O1078" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1079" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1079" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1079" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1079" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1079" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1079" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1079" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1079" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1079" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1079" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1079" s="6"/>
+      <c r="L1079" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1079" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1079" s="6">
+        <v>180</v>
+      </c>
+      <c r="O1079" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1080" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1080" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1080" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1080" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1080" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1080" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1080" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1080" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1080" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1080" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1080" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1080" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1080" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1080" s="6">
+        <v>168</v>
+      </c>
+      <c r="O1080" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1081" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1081" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1081" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1081" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1081" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1081" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1081" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1081" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1081" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1081" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1081" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1081" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1081" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1081" s="6">
+        <v>180</v>
+      </c>
+      <c r="O1081" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1082" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1082" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1082" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1082" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1082" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1082" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1082" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1082" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1082" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1082" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1082" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1082" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1082" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1082" s="6">
+        <v>176</v>
+      </c>
+      <c r="O1082" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1083" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1083" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1083" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1083" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1083" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1083" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1083" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1083" s="6">
+        <v>3</v>
+      </c>
+      <c r="I1083" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1083" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1083" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1083" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1083" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1083" s="6">
+        <v>170</v>
+      </c>
+      <c r="O1083" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1084" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1084" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1084" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1084" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1084" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1084" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1084" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1084" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1084" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1084" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1084" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1084" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1084" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1084" s="6">
+        <v>166</v>
+      </c>
+      <c r="O1084" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1085" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1085" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1085" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1085" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1085" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1085" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1085" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1085" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1085" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1085" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1085" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1085" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1085" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1085" s="6">
+        <v>166</v>
+      </c>
+      <c r="O1085" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1086" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1086" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1086" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1086" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1086" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1086" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1086" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1086" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1086" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1086" s="6">
+        <v>3</v>
+      </c>
+      <c r="K1086" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1086" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1086" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1086" s="6">
+        <v>186</v>
+      </c>
+      <c r="O1086" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1087" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1087" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1087" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1087" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1087" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1087" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1087" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1087" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1087" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1087" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1087" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1087" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1087" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1087" s="6">
+        <v>182</v>
+      </c>
+      <c r="O1087" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1088" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1088" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1088" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1088" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1088" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1088" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1088" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1088" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1088" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1088" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1088" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1088" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1088" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1088" s="6">
+        <v>175</v>
+      </c>
+      <c r="O1088" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1089" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1089" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1089" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1089" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1089" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1089" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1089" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1089" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1089" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1089" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1089" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1089" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1089" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1089" s="6">
+        <v>184</v>
+      </c>
+      <c r="O1089" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1090" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1090" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1090" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1090" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1090" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1090" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1090" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1090" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1090" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1090" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1090" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1090" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1090" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1090" s="6">
+        <v>180</v>
+      </c>
+      <c r="O1090" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1091" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1091" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1091" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1091" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1091" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1091" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1091" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1091" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1091" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1091" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1091" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1091" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1091" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1091" s="6">
+        <v>165</v>
+      </c>
+      <c r="O1091" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1092" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1092" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1092" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1092" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1092" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1092" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1092" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1092" s="6">
+        <v>3</v>
+      </c>
+      <c r="I1092" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1092" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1092" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1092" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1092" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1092" s="6">
+        <v>188</v>
+      </c>
+      <c r="O1092" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1093" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1093" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1093" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1093" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1093" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1093" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1093" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1093" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1093" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1093" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1093" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1093" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1093" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1093" s="6">
+        <v>183</v>
+      </c>
+      <c r="O1093" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1094" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1094" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1094" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1094" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1094" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1094" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1094" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1094" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1094" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1094" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1094" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1094" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1094" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1094" s="6">
+        <v>169</v>
+      </c>
+      <c r="O1094" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1095" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1095" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1095" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1095" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1095" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1095" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1095" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1095" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1095" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1095" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1095" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1095" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1095" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1095" s="6">
+        <v>178</v>
+      </c>
+      <c r="O1095" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1096" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1096" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1096" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1096" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1096" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1096" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1096" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1096" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1096" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1096" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1096" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1096" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1096" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1096" s="6">
+        <v>175</v>
+      </c>
+      <c r="O1096" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1097" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1097" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1097" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1097" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1097" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1097" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1097" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1097" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1097" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1097" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1097" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1097" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1097" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1097" s="6">
+        <v>172</v>
+      </c>
+      <c r="O1097" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1098" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1098" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1098" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1098" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1098" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1098" s="6">
+        <v>4</v>
+      </c>
+      <c r="G1098" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1098" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1098" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1098" s="6">
+        <v>3</v>
+      </c>
+      <c r="K1098" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1098" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1098" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1098" s="6">
+        <v>172</v>
+      </c>
+      <c r="O1098" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1099" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1099" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1099" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1099" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1099" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1099" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1099" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1099" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1099" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1099" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1099" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1099" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1099" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1099" s="6">
+        <v>174</v>
+      </c>
+      <c r="O1099" s="6">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/data/gummibears.xlsx
+++ b/data/gummibears.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D75E7B4-F93B-7149-9320-FDA4ED612143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CC6A40-A146-5444-A2B6-837FF40458B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2300" yWindow="600" windowWidth="30960" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="31">
   <si>
     <t>m</t>
   </si>
@@ -121,6 +123,9 @@
   </si>
   <si>
     <t>Modellierung_landwirtschaftlicher_Daten</t>
+  </si>
+  <si>
+    <t>Angewandte Statistik</t>
   </si>
 </sst>
 </file>
@@ -643,7 +648,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q1099"/>
+  <dimension ref="A1:Q1135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -51317,6 +51322,1684 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1100" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1100" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1100" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1100" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1100" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1100" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1100" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1100" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1100" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1100" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1100" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1100" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1100" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1100" s="6">
+        <v>26</v>
+      </c>
+      <c r="N1100" s="6">
+        <v>177</v>
+      </c>
+      <c r="O1100" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1101" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1101" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1101" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1101" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1101" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1101" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1101" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1101" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1101" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1101" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1101" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1101" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1101" s="6">
+        <v>27</v>
+      </c>
+      <c r="N1101" s="6">
+        <v>187</v>
+      </c>
+      <c r="O1101" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1102" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1102" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1102" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1102" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1102" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1102" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1102" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1102" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1102" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1102" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1102" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1102" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1102" s="6">
+        <v>27</v>
+      </c>
+      <c r="N1102" s="6">
+        <v>171</v>
+      </c>
+      <c r="O1102" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1103" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1103" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1103" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1103" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1103" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1103" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1103" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1103" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1103" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1103" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1103" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1103" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1103" s="6">
+        <v>25</v>
+      </c>
+      <c r="N1103" s="6">
+        <v>197</v>
+      </c>
+      <c r="O1103" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1104" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1104" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1104" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1104" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1104" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1104" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1104" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1104" s="6">
+        <v>4</v>
+      </c>
+      <c r="I1104" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1104" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1104" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1104" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1104" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1104" s="6">
+        <v>181</v>
+      </c>
+      <c r="O1104" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1105" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1105" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1105" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1105" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1105" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1105" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1105" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1105" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1105" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1105" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1105" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1105" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1105" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1105" s="6">
+        <v>169</v>
+      </c>
+      <c r="O1105" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1106" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1106" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1106" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1106" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1106" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1106" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1106" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1106" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1106" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1106" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1106" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1106" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1106" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1106" s="6">
+        <v>176</v>
+      </c>
+      <c r="O1106" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1107" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1107" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1107" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1107" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1107" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1107" s="6">
+        <v>4</v>
+      </c>
+      <c r="G1107" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1107" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1107" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1107" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1107" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1107" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1107" s="6">
+        <v>25</v>
+      </c>
+      <c r="N1107" s="6">
+        <v>188</v>
+      </c>
+      <c r="O1107" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1108" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1108" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1108" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1108" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1108" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1108" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1108" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1108" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1108" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1108" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1108" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1108" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1108" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1108" s="6">
+        <v>160</v>
+      </c>
+      <c r="O1108" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1109" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1109" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1109" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1109" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1109" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1109" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1109" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1109" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1109" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1109" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1109" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1109" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1109" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1109" s="6">
+        <v>189</v>
+      </c>
+      <c r="O1109" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1110" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1110" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1110" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1110" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1110" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1110" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1110" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1110" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1110" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1110" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1110" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1110" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1110" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1110" s="6">
+        <v>175</v>
+      </c>
+      <c r="O1110" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1111" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1111" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1111" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1111" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1111" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1111" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1111" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1111" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1111" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1111" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1111" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1111" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1111" s="6">
+        <v>28</v>
+      </c>
+      <c r="N1111" s="6">
+        <v>168</v>
+      </c>
+      <c r="O1111" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1112" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1112" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1112" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1112" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1112" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1112" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1112" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1112" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1112" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1112" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1112" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1112" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1112" s="6">
+        <v>26</v>
+      </c>
+      <c r="N1112" s="6">
+        <v>188</v>
+      </c>
+      <c r="O1112" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1113" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1113" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1113" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1113" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1113" s="6">
+        <v>4</v>
+      </c>
+      <c r="F1113" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1113" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1113" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1113" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1113" s="6">
+        <v>3</v>
+      </c>
+      <c r="K1113" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1113" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1113" s="6">
+        <v>21</v>
+      </c>
+      <c r="N1113" s="6">
+        <v>185</v>
+      </c>
+      <c r="O1113" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1114" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1114" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1114" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1114" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1114" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1114" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1114" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1114" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1114" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1114" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1114" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1114" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1114" s="6">
+        <v>25</v>
+      </c>
+      <c r="N1114" s="6">
+        <v>195</v>
+      </c>
+      <c r="O1114" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1115" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1115" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1115" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1115" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1115" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1115" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1115" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1115" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1115" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1115" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1115" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1115" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1115" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1115" s="6">
+        <v>168</v>
+      </c>
+      <c r="O1115" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1116" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1116" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1116" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1116" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1116" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1116" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1116" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1116" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1116" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1116" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1116" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1116" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1116" s="6">
+        <v>27</v>
+      </c>
+      <c r="N1116" s="6">
+        <v>178</v>
+      </c>
+      <c r="O1116" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1117" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1117" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1117" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1117" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1117" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1117" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1117" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1117" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1117" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1117" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1117" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1117" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1117" s="6">
+        <v>25</v>
+      </c>
+      <c r="N1117" s="6">
+        <v>185</v>
+      </c>
+      <c r="O1117" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1118" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1118" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1118" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1118" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1118" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1118" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1118" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1118" s="6">
+        <v>3</v>
+      </c>
+      <c r="I1118" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1118" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1118" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1118" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1118" s="6">
+        <v>27</v>
+      </c>
+      <c r="N1118" s="6">
+        <v>170</v>
+      </c>
+      <c r="O1118" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1119" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1119" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1119" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1119" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1119" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1119" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1119" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1119" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1119" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1119" s="6">
+        <v>3</v>
+      </c>
+      <c r="K1119" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1119" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1119" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1119" s="6">
+        <v>185</v>
+      </c>
+      <c r="O1119" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1120" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1120" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1120" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1120" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1120" s="6">
+        <v>4</v>
+      </c>
+      <c r="F1120" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1120" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1120" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1120" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1120" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1120" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1120" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1120" s="6">
+        <v>28</v>
+      </c>
+      <c r="N1120" s="6">
+        <v>172</v>
+      </c>
+      <c r="O1120" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1121" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1121" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1121" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1121" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1121" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1121" s="6">
+        <v>7</v>
+      </c>
+      <c r="G1121" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1121" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1121" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1121" s="6">
+        <v>3</v>
+      </c>
+      <c r="K1121" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1121" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1121" s="6">
+        <v>26</v>
+      </c>
+      <c r="N1121" s="6">
+        <v>172</v>
+      </c>
+      <c r="O1121" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1122" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1122" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1122" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1122" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1122" s="6">
+        <v>0</v>
+      </c>
+      <c r="G1122" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1122" s="6">
+        <v>4</v>
+      </c>
+      <c r="I1122" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1122" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1122" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1122" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1122" s="6">
+        <v>26</v>
+      </c>
+      <c r="N1122" s="6">
+        <v>182</v>
+      </c>
+      <c r="O1122" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1123" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1123" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1123" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1123" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1123" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1123" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1123" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1123" s="6">
+        <v>4</v>
+      </c>
+      <c r="I1123" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1123" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1123" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1123" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1123" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1123" s="6">
+        <v>185</v>
+      </c>
+      <c r="O1123" s="6"/>
+    </row>
+    <row r="1124" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1124" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1124" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1124" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1124" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1124" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1124" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1124" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1124" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1124" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1124" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1124" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1124" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1124" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1124" s="6">
+        <v>173</v>
+      </c>
+      <c r="O1124" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1125" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1125" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1125" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1125" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1125" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1125" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1125" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1125" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1125" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1125" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1125" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1125" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1125" s="6">
+        <v>26</v>
+      </c>
+      <c r="N1125" s="6">
+        <v>166</v>
+      </c>
+      <c r="O1125" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1126" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1126" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1126" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1126" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1126" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1126" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1126" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1126" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1126" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1126" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1126" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1126" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1126" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1126" s="6">
+        <v>196</v>
+      </c>
+      <c r="O1126" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1127" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1127" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1127" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1127" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1127" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1127" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1127" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1127" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1127" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1127" s="6"/>
+      <c r="K1127" s="6"/>
+      <c r="L1127" s="6"/>
+      <c r="M1127" s="6"/>
+      <c r="N1127" s="6"/>
+      <c r="O1127" s="6"/>
+    </row>
+    <row r="1128" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1128" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1128" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1128" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1128" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1128" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1128" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1128" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1128" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1128" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1128" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1128" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1128" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1128" s="6">
+        <v>25</v>
+      </c>
+      <c r="N1128" s="6">
+        <v>190</v>
+      </c>
+      <c r="O1128" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1129" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1129" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1129" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1129" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1129" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1129" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1129" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1129" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1129" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1129" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1129" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1129" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1129" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1129" s="6">
+        <v>182</v>
+      </c>
+      <c r="O1129" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1130" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1130" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1130" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1130" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1130" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1130" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1130" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1130" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1130" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1130" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1130" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1130" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1130" s="6">
+        <v>31</v>
+      </c>
+      <c r="N1130" s="6">
+        <v>175</v>
+      </c>
+      <c r="O1130" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1131" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1131" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1131" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1131" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1131" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1131" s="6">
+        <v>5</v>
+      </c>
+      <c r="G1131" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1131" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1131" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1131" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1131" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1131" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1131" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1131" s="6">
+        <v>167</v>
+      </c>
+      <c r="O1131" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1132" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1132" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1132" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1132" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1132" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1132" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1132" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1132" s="6">
+        <v>4</v>
+      </c>
+      <c r="I1132" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1132" s="6">
+        <v>3</v>
+      </c>
+      <c r="K1132" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1132" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1132" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1132" s="6">
+        <v>161</v>
+      </c>
+      <c r="O1132" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1133" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1133" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1133" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1133" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1133" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1133" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1133" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1133" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1133" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1133" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1133" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1133" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1133" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1133" s="6">
+        <v>172</v>
+      </c>
+      <c r="O1133" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1134" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1134" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1134" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1134" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1134" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1134" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1134" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1134" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1134" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1134" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1134" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1134" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1134" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1134" s="6">
+        <v>182</v>
+      </c>
+      <c r="O1134" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1135" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1135" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1135" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1135" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1135" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1135" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1135" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1135" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1135" s="6">
+        <v>10</v>
+      </c>
+      <c r="J1135" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1135" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1135" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1135" s="6">
+        <v>28</v>
+      </c>
+      <c r="N1135" s="6">
+        <v>175</v>
+      </c>
+      <c r="O1135" s="6">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
